--- a/results/greedy/UAVs3_GRID13/tour/UAVs3_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs3_GRID13/tour/UAVs3_GRID13_1920_16_Greedy_sequences.xlsx
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04157737497007474</v>
+        <v>0.04057554103201255</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05126883299089968</v>
+        <v>0.05025791696971282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04401412501465529</v>
+        <v>0.04265837499406189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04142374999355525</v>
+        <v>0.04019887500908226</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03457016695756465</v>
+        <v>0.03444374998798594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04023587499978021</v>
+        <v>0.04006304102949798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04133091599214822</v>
+        <v>0.04112254199571908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03728645900264382</v>
+        <v>0.03536362497834489</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03468074998818338</v>
+        <v>0.0327547499909997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03495075000682846</v>
+        <v>0.03231058298842981</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03821562498342246</v>
+        <v>0.03604250005446374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03720095800235868</v>
+        <v>0.03595679200952873</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0472707090084441</v>
+        <v>0.04705858399393037</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0311234169639647</v>
+        <v>0.02972016698913649</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03800512501038611</v>
+        <v>0.03624429198680446</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03959429101087153</v>
+        <v>0.03839462500764057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03986291703768075</v>
+        <v>0.03789637499721721</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03358179202768952</v>
+        <v>0.03161416703369468</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04187824996188283</v>
+        <v>0.04045108403079212</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04191987501690164</v>
+        <v>0.04123529099160805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03607045899843797</v>
+        <v>0.03452637494774535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03606208297424018</v>
+        <v>0.03471866599284112</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04459554102504626</v>
+        <v>0.04379962495295331</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04765087499981746</v>
+        <v>0.04598954197717831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04042779200244695</v>
+        <v>0.03936875000363216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04486270796041936</v>
+        <v>0.04423450003378093</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03215516603086144</v>
+        <v>0.0306902079610154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05133354204008356</v>
+        <v>0.0504038329818286</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03562999999849126</v>
+        <v>0.03417104104300961</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04405237501487136</v>
+        <v>0.0420905000064522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02814825001405552</v>
+        <v>0.02718516701133922</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03221237502293661</v>
+        <v>0.03038287500385195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03137462504673749</v>
+        <v>0.02959637501044199</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03911145799793303</v>
+        <v>0.03702008299296722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04659508302574977</v>
+        <v>0.04594495904166251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04184025002177805</v>
+        <v>0.04057312500663102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04005058301845565</v>
+        <v>0.03819649998331442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04662866704165936</v>
+        <v>0.04508595902007073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03368045797105879</v>
+        <v>0.03285329102072865</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03619095799513161</v>
+        <v>0.03400520799914375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05002033297205344</v>
+        <v>0.04826412495458499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0437294160365127</v>
+        <v>0.04213795799296349</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02800704096443951</v>
+        <v>0.02706191700417548</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03841529099736363</v>
+        <v>0.03640562499640509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04679783299798146</v>
+        <v>0.04480412497650832</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03998233302263543</v>
+        <v>0.03902062500128523</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04289216600591317</v>
+        <v>0.04158483300125226</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0399907500250265</v>
+        <v>0.03861529100686312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04053316701902077</v>
+        <v>0.03938795800786465</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0306493749958463</v>
+        <v>0.02891591697698459</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03213766601402313</v>
+        <v>0.03032045799773186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03656762500759214</v>
+        <v>0.03521054203156382</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04075216699857265</v>
+        <v>0.03888750000623986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03679383301641792</v>
+        <v>0.03508420899743214</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03651887498563156</v>
+        <v>0.03525129199260846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04299379099393263</v>
+        <v>0.04170795902609825</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04058666701894253</v>
+        <v>0.04008087498368695</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03368608298478648</v>
+        <v>0.03220170800341293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04796458303462714</v>
+        <v>0.04596800002036616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0371515000006184</v>
+        <v>0.03674866701476276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04677133297082037</v>
+        <v>0.04547241702675819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03796887502539903</v>
+        <v>0.03739499999210238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03649958403548226</v>
+        <v>0.03511774999788031</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0478182079968974</v>
+        <v>0.04617574997246265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05120912496931851</v>
+        <v>0.04961320798611268</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0378476670011878</v>
+        <v>0.03642462502466515</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03739554196363315</v>
+        <v>0.03544887498719618</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04015524999704212</v>
+        <v>0.04010445799212903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03122662496753037</v>
+        <v>0.0298972079763189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03379087499342859</v>
+        <v>0.03190812497632578</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03317266696831211</v>
+        <v>0.0318280829815194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03130312502617016</v>
+        <v>0.03110000002197921</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03529712499585003</v>
+        <v>0.03430304198991507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04691633401671425</v>
+        <v>0.04560787498485297</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0363181249704212</v>
+        <v>0.03534279204905033</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03392591699957848</v>
+        <v>0.03360299998894334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02985629200702533</v>
+        <v>0.02889795799273998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04666062496835366</v>
+        <v>0.04599579202476889</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03275829198537394</v>
+        <v>0.03490179200889543</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.036027499998454</v>
+        <v>0.03586145804729313</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03600258298683912</v>
+        <v>0.03610779100563377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.039083749987185</v>
+        <v>0.03845449996879324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03904324996983632</v>
+        <v>0.03870995796751231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04574091598624364</v>
+        <v>0.04471737495623529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04280629096319899</v>
+        <v>0.04181808297289535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03889324999181554</v>
+        <v>0.03724962496198714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02805187500780448</v>
+        <v>0.02761045802617446</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.031467207998503</v>
+        <v>0.0320171249913983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03842366696335375</v>
+        <v>0.03774879203410819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04092266695806757</v>
+        <v>0.04105724999681115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04578570794546977</v>
+        <v>0.04518666700460017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03490816702833399</v>
+        <v>0.03418783302186057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03548295801738277</v>
+        <v>0.03517049999209121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04067708301590756</v>
+        <v>0.04074162500910461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05038274999242276</v>
+        <v>0.04861541697755456</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03359962505055591</v>
+        <v>0.03345899999840185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04514262499287724</v>
+        <v>0.04425237502437085</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03600333305075765</v>
+        <v>0.03500858403276652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03479233401594684</v>
+        <v>0.03429745795438066</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03812283300794661</v>
+        <v>0.03758775000460446</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/results/greedy/UAVs3_GRID13/tour/UAVs3_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs3_GRID13/tour/UAVs3_GRID13_1920_16_Greedy_sequences.xlsx
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04057554103201255</v>
+        <v>0.04089891701005399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05025791696971282</v>
+        <v>0.05089683301048353</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04265837499406189</v>
+        <v>0.04331287497188896</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04019887500908226</v>
+        <v>0.03898566600400954</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03444374998798594</v>
+        <v>0.03417620802065358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04006304102949798</v>
+        <v>0.0401328339939937</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04112254199571908</v>
+        <v>0.04037762497318909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03536362497834489</v>
+        <v>0.03692554199369624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0327547499909997</v>
+        <v>0.0342610829975456</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03231058298842981</v>
+        <v>0.03434504196047783</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03604250005446374</v>
+        <v>0.03749166696798056</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03595679200952873</v>
+        <v>0.03652491699904203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04705858399393037</v>
+        <v>0.04544374998658895</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02972016698913649</v>
+        <v>0.03108158300165087</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03624429198680446</v>
+        <v>0.0372937920037657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03839462500764057</v>
+        <v>0.03787854197435081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03789637499721721</v>
+        <v>0.03938737499993294</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03161416703369468</v>
+        <v>0.03302287502447143</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04045108403079212</v>
+        <v>0.04120879201218486</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04123529099160805</v>
+        <v>0.04143149999435991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03452637494774535</v>
+        <v>0.03555699996650219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03471866599284112</v>
+        <v>0.035563874989748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04379962495295331</v>
+        <v>0.0439442089991644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04598954197717831</v>
+        <v>0.04488104104530066</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03936875000363216</v>
+        <v>0.03918579203309491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04423450003378093</v>
+        <v>0.04408833401976153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0306902079610154</v>
+        <v>0.03130479203537107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0504038329818286</v>
+        <v>0.05040912498952821</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03417104104300961</v>
+        <v>0.03493154200259596</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0420905000064522</v>
+        <v>0.04347029194468632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02718516701133922</v>
+        <v>0.02793691598344594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03038287500385195</v>
+        <v>0.03177083301125094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02959637501044199</v>
+        <v>0.03073991602286696</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03702008299296722</v>
+        <v>0.03800829203100875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04594495904166251</v>
+        <v>0.04477379197487608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04057312500663102</v>
+        <v>0.04114587494404987</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03819649998331442</v>
+        <v>0.03915370901813731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04508595902007073</v>
+        <v>0.04522562498459592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03285329102072865</v>
+        <v>0.03337658400414512</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03400520799914375</v>
+        <v>0.03587841603439301</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04826412495458499</v>
+        <v>0.04943174996878952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04213795799296349</v>
+        <v>0.04345162503886968</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02706191700417548</v>
+        <v>0.02746387495426461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03640562499640509</v>
+        <v>0.03717649995815009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04480412497650832</v>
+        <v>0.04610024997964501</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03902062500128523</v>
+        <v>0.03855020803166553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04158483300125226</v>
+        <v>0.0420264580170624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03861529100686312</v>
+        <v>0.03911012498429045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03938795800786465</v>
+        <v>0.03931412496604025</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02891591697698459</v>
+        <v>0.02982345799682662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03032045799773186</v>
+        <v>0.03150250000180677</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03521054203156382</v>
+        <v>0.06440891703823581</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03888750000623986</v>
+        <v>0.04025841702241451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03508420899743214</v>
+        <v>0.0348570829955861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03525129199260846</v>
+        <v>0.0354312079725787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04170795902609825</v>
+        <v>0.04245662502944469</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04008087498368695</v>
+        <v>0.03925991599680856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03220170800341293</v>
+        <v>0.03345183399505913</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04596800002036616</v>
+        <v>0.04705674998695031</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03674866701476276</v>
+        <v>0.03748387499945238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04547241702675819</v>
+        <v>0.04565870895748958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03739499999210238</v>
+        <v>0.0366583329741843</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03511774999788031</v>
+        <v>0.03581245796522126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04617574997246265</v>
+        <v>0.04703316697850823</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04961320798611268</v>
+        <v>0.05053558299550787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03642462502466515</v>
+        <v>0.03788420901400968</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03544887498719618</v>
+        <v>0.03575741598615423</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04010445799212903</v>
+        <v>0.03815954102901742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0298972079763189</v>
+        <v>0.03083054098533466</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03190812497632578</v>
+        <v>0.03316812502453104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0318280829815194</v>
+        <v>0.03252025000983849</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03110000002197921</v>
+        <v>0.03081433300394565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03430304198991507</v>
+        <v>0.03517854202073067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04560787498485297</v>
+        <v>0.04677575000096112</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03534279204905033</v>
+        <v>0.0361100829904899</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03360299998894334</v>
+        <v>0.03317016700748354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02889795799273998</v>
+        <v>0.02917508396785706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04599579202476889</v>
+        <v>0.04656712501309812</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03490179200889543</v>
+        <v>0.03239312500227243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03586145804729313</v>
+        <v>0.03605225001228973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03610779100563377</v>
+        <v>0.03736966702854261</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03845449996879324</v>
+        <v>0.03896316699683666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03870995796751231</v>
+        <v>0.03864525002427399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04471737495623529</v>
+        <v>0.04548920900560915</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04181808297289535</v>
+        <v>0.04327625001315027</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03724962496198714</v>
+        <v>0.03919700003461912</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761045802617446</v>
+        <v>0.0277905419934541</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0320171249913983</v>
+        <v>0.03092295798705891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03774879203410819</v>
+        <v>0.03803787502693012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04105724999681115</v>
+        <v>0.04100270796334371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04518666700460017</v>
+        <v>0.04553158296039328</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03418783302186057</v>
+        <v>0.03432108298875391</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03517049999209121</v>
+        <v>0.03476045798743144</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04074162500910461</v>
+        <v>0.04078537499299273</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04861541697755456</v>
+        <v>0.04909037501784042</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03345899999840185</v>
+        <v>0.03316912497393787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04425237502437085</v>
+        <v>0.04379837500164285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03500858403276652</v>
+        <v>0.03499008301878348</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03429745795438066</v>
+        <v>0.03381537494715303</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03758775000460446</v>
+        <v>0.03756062500178814</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
